--- a/Team-Data/2008-09/3-28-2008-09.xlsx
+++ b/Team-Data/2008-09/3-28-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -769,19 +836,19 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -790,16 +857,16 @@
         <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>5</v>
@@ -808,10 +875,10 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.74</v>
+        <v>0.743</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.393</v>
       </c>
       <c r="O3" t="n">
         <v>19.7</v>
       </c>
       <c r="P3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
@@ -903,25 +970,25 @@
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -957,13 +1024,13 @@
         <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>5</v>
@@ -981,10 +1048,10 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.452</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1055,10 +1122,10 @@
         <v>16.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
         <v>23.9</v>
@@ -1067,19 +1134,19 @@
         <v>0.741</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1091,19 +1158,19 @@
         <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,16 +1191,16 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM4" t="n">
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1142,19 +1209,19 @@
         <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
         <v>26</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1289,10 @@
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
         <v>0.454</v>
@@ -1237,55 +1304,55 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0.792</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
         <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1294,10 +1361,10 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1309,28 +1376,28 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,13 +1406,13 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,14 +1421,14 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
         <v>16</v>
       </c>
-      <c r="BB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>17</v>
-      </c>
       <c r="BD5" t="n">
         <v>10</v>
       </c>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.831</v>
+        <v>0.819</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
@@ -1440,10 +1507,10 @@
         <v>41.9</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
@@ -1455,19 +1522,19 @@
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,10 +1549,10 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1497,10 +1564,10 @@
         <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1509,25 +1576,25 @@
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>23</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
@@ -1536,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1673,16 +1740,16 @@
         <v>11</v>
       </c>
       <c r="AL7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM7" t="n">
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>28</v>
@@ -1694,16 +1761,16 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1712,7 +1779,7 @@
         <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.649</v>
+        <v>0.644</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
@@ -1792,49 +1859,49 @@
         <v>30.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
         <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T8" t="n">
         <v>41.5</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.8</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1870,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
         <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>25</v>
@@ -1891,19 +1958,19 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.486</v>
+        <v>0.479</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1959,13 +2026,13 @@
         <v>0.454</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M9" t="n">
         <v>12.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
         <v>16.8</v>
@@ -1974,7 +2041,7 @@
         <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R9" t="n">
         <v>11.5</v>
@@ -1983,10 +2050,10 @@
         <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V9" t="n">
         <v>11.9</v>
@@ -1995,7 +2062,7 @@
         <v>6.2</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
         <v>4.2</v>
@@ -2013,19 +2080,19 @@
         <v>-0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2058,7 +2125,7 @@
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
         <v>18</v>
@@ -2070,25 +2137,25 @@
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.342</v>
+        <v>0.347</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O10" t="n">
         <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R10" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
@@ -2180,22 +2247,22 @@
         <v>6.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
         <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.6</v>
+        <v>108.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2219,7 +2286,7 @@
         <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
@@ -2234,22 +2301,22 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -2299,52 +2366,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.649</v>
+        <v>0.644</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
         <v>7.6</v>
       </c>
       <c r="M11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N11" t="n">
         <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P11" t="n">
         <v>23.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T11" t="n">
         <v>42.9</v>
@@ -2371,16 +2438,16 @@
         <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2389,10 +2456,10 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
         <v>21</v>
@@ -2410,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2431,22 +2498,22 @@
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
         <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.411</v>
+        <v>0.417</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J12" t="n">
-        <v>86.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.45</v>
@@ -2514,10 +2581,10 @@
         <v>0.375</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
         <v>0.805</v>
@@ -2535,43 +2602,43 @@
         <v>21.7</v>
       </c>
       <c r="V12" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
         <v>103.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2592,16 +2659,16 @@
         <v>10</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2613,25 +2680,25 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="n">
         <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>0.243</v>
+        <v>0.247</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2684,16 +2751,16 @@
         <v>81.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L13" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O13" t="n">
         <v>17</v>
@@ -2702,22 +2769,22 @@
         <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R13" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T13" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2726,7 +2793,7 @@
         <v>5.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z13" t="n">
         <v>20.2</v>
@@ -2735,13 +2802,13 @@
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2777,31 +2844,31 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR13" t="n">
         <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY13" t="n">
         <v>21</v>
@@ -2816,7 +2883,7 @@
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,16 +2939,16 @@
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P14" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.769</v>
@@ -2890,10 +2957,10 @@
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>107.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2947,28 +3014,28 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2980,16 +3047,16 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J15" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
         <v>10.5</v>
       </c>
       <c r="S15" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="T15" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="U15" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3099,19 +3166,19 @@
         <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3147,7 +3214,7 @@
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
         <v>29</v>
@@ -3162,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
         <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>0.534</v>
+        <v>0.528</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J16" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K16" t="n">
         <v>0.455</v>
@@ -3239,25 +3306,25 @@
         <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
         <v>17.4</v>
       </c>
       <c r="P16" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
@@ -3278,16 +3345,16 @@
         <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3305,40 +3372,40 @@
         <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM16" t="n">
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3347,10 +3414,10 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -3406,28 +3473,28 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.782</v>
@@ -3436,16 +3503,16 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U17" t="n">
         <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.3</v>
@@ -3457,19 +3524,19 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
         <v>-1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3484,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3499,13 +3566,13 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,25 +3581,25 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,10 +3730,10 @@
         <v>26</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3681,31 +3748,31 @@
         <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="n">
         <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
         <v>22</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
@@ -3848,7 +3915,7 @@
         <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -3857,16 +3924,16 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
@@ -3881,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
@@ -3890,7 +3957,7 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG20" t="n">
         <v>9</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>10</v>
@@ -4045,10 +4112,10 @@
         <v>13</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4119,31 +4186,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
         <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.397</v>
+        <v>0.403</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L21" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M21" t="n">
         <v>28.4</v>
@@ -4152,22 +4219,22 @@
         <v>0.361</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0.788</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T21" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.2</v>
@@ -4179,7 +4246,7 @@
         <v>7.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
         <v>5.3</v>
@@ -4188,16 +4255,16 @@
         <v>20.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.6</v>
+        <v>105.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4221,16 +4288,16 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>21</v>
@@ -4248,7 +4315,7 @@
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>25</v>
@@ -4391,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>6</v>
@@ -4418,13 +4485,13 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
         <v>5</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4448,7 +4515,7 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
@@ -4573,13 +4640,13 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4615,13 +4682,13 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>20</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4755,10 +4822,10 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4788,13 +4855,13 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -4847,55 +4914,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
         <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>0.548</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I25" t="n">
         <v>41</v>
       </c>
       <c r="J25" t="n">
-        <v>81.3</v>
+        <v>81</v>
       </c>
       <c r="K25" t="n">
-        <v>0.504</v>
+        <v>0.507</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>23.1</v>
@@ -4904,7 +4971,7 @@
         <v>15.7</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X25" t="n">
         <v>5.1</v>
@@ -4913,19 +4980,19 @@
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA25" t="n">
         <v>22.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>108.9</v>
+        <v>109</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,13 +5004,13 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
         <v>5</v>
@@ -4967,13 +5034,13 @@
         <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
         <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5032,52 +5099,52 @@
         <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.639</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5086,13 +5153,13 @@
         <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X26" t="n">
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
         <v>20.6</v>
@@ -5101,19 +5168,19 @@
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
         <v>8</v>
@@ -5137,16 +5204,16 @@
         <v>11</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,10 +5222,10 @@
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5319,7 +5386,7 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>10</v>
@@ -5501,7 +5568,7 @@
         <v>9</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -5546,7 +5613,7 @@
         <v>24</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5665,10 +5732,10 @@
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ29" t="n">
         <v>16</v>
@@ -5686,7 +5753,7 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
         <v>26</v>
@@ -5704,7 +5771,7 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="H30" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
         <v>38.5</v>
@@ -5784,16 +5851,16 @@
         <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N30" t="n">
         <v>0.347</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="P30" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="Q30" t="n">
         <v>0.77</v>
@@ -5802,16 +5869,16 @@
         <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U30" t="n">
         <v>24.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>8.699999999999999</v>
@@ -5826,28 +5893,28 @@
         <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB30" t="n">
         <v>103.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
         <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG30" t="n">
         <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,25 +5941,25 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT30" t="n">
         <v>17</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
@@ -5904,7 +5971,7 @@
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
         <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" t="n">
-        <v>0.23</v>
+        <v>0.233</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5981,7 +6048,7 @@
         <v>0.766</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
         <v>28.1</v>
@@ -5990,19 +6057,19 @@
         <v>39.9</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z31" t="n">
         <v>20.6</v>
@@ -6014,22 +6081,22 @@
         <v>95.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6077,16 +6144,16 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-28-2008-09</t>
+          <t>2009-03-28</t>
         </is>
       </c>
     </row>
